--- a/project_task.xlsx
+++ b/project_task.xlsx
@@ -419,27 +419,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>task_id</t>
+          <t>task_task_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>project_name</t>
+          <t>task_project_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>task_assigned_to</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>task_status</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>hours_logged</t>
+          <t>task_hours_logged</t>
         </is>
       </c>
     </row>
@@ -464,8 +464,10 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>35</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -489,8 +491,10 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>18</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -514,8 +518,10 @@
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/project_task.xlsx
+++ b/project_task.xlsx
@@ -419,27 +419,27 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>task_task_id</t>
+          <t>task_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>task_project_name</t>
+          <t>project_name</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>task_assigned_to</t>
+          <t>assigned_to</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>task_status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>task_hours_logged</t>
+          <t>hours_logged</t>
         </is>
       </c>
     </row>
